--- a/output/full_scan/batch_seq1_2026-09-04.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-04.xlsx
@@ -527,94 +527,94 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1563</v>
+        <v>1402</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1030.629404870625</v>
+        <v>1054.322063973672</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>66</v>
+        <v>29.15</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.98512600823695</v>
+        <v>58.17249268732858</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17.57465411627794</v>
+        <v>24.47149690535824</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.194834990775525</v>
+        <v>0.3287989958635952</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.6475740031296546</v>
+        <v>0.0519615152974565</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1236</v>
+        <v>1563</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>737.1539448268946</v>
+        <v>1030.629404870625</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.15</v>
+        <v>66</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.88258706532734</v>
+        <v>59.98512605287677</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.69324095326376</v>
+        <v>17.57465407975327</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.9259877200704444</v>
+        <v>2.194834990775525</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0407475030812332</v>
+        <v>0.6475740029334669</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1402</v>
+        <v>1558</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>724.3220639736718</v>
+        <v>905.3561280736408</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.15</v>
+        <v>106.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>58.17249307311382</v>
+        <v>72.72778470784114</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24.47149688340978</v>
+        <v>34.14072716223759</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3287989958635952</v>
+        <v>0.5589694183748237</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0519615154023922</v>
+        <v>0.3512333162930829</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1319</v>
+        <v>1101</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>687.7401414539611</v>
+        <v>830.2737102051273</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.7496424067523</v>
+        <v>52.71969000087731</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33.35390863539189</v>
+        <v>29.96600475284142</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6400684531930464</v>
+        <v>0.327371020512726</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.0746671820386559</v>
+        <v>0.0043640727795548</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1110</v>
+        <v>1236</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>660.6450421276783</v>
+        <v>812.1539448268946</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.3</v>
+        <v>26.15</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.57874857235129</v>
+        <v>68.88258706532734</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23.09450409998217</v>
+        <v>26.69324089746896</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9127642753577702</v>
+        <v>0.9259877200704444</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0121415359939262</v>
+        <v>0.0407475030907704</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1558</v>
+        <v>1319</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>655.3561280736408</v>
+        <v>802.7401414539611</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>106.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>72.72778470784114</v>
+        <v>58.74964258957412</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.14072714188737</v>
+        <v>33.35390866858949</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5589694183748237</v>
+        <v>0.6400684531930464</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3512333162930829</v>
+        <v>-0.07466718184785941</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1303</v>
+        <v>1326</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>644.1085645981417</v>
+        <v>800.9864931283543</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>225.5</v>
+        <v>69.8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.06717279109262</v>
+        <v>61.43310846569564</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.53475461064177</v>
+        <v>23.35385045582583</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6310530529484822</v>
+        <v>1.127576680795168</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,11 +888,11 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.240409168638736</v>
+        <v>1.345058626165756</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>628.7091526091151</v>
+        <v>798.709152609115</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>48.7</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.77833553847712</v>
+        <v>62.77833561182289</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.33010521563791</v>
+        <v>25.33010521546371</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.421229075593835</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.464213460821179</v>
+        <v>0.4642134608688717</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1232</v>
+        <v>1110</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>607.1709520275838</v>
+        <v>795.6450421276783</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>157</v>
+        <v>16.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>55.1182519125703</v>
+        <v>59.57874882329268</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27.04379901993858</v>
+        <v>23.0945041552983</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7106638699729712</v>
+        <v>0.9127642753577702</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1545794224487104</v>
+        <v>0.0121415359462296</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1440</v>
+        <v>1102</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>601.1020539705069</v>
+        <v>792.190213179861</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.9</v>
+        <v>35.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.05404644242947</v>
+        <v>60.18913070182904</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.57177554090341</v>
+        <v>24.21986895855195</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.816863657943175</v>
+        <v>0.4135146574790697</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0358360689165666</v>
+        <v>0.1119209058677342</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1326</v>
+        <v>1440</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>600.9864931283543</v>
+        <v>791.102053970507</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.8</v>
+        <v>13.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.43310848368728</v>
+        <v>57.05404636768839</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23.35385051117022</v>
+        <v>26.57177555182396</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.127576680795168</v>
+        <v>1.816863657943175</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.34505862601312</v>
+        <v>0.0358360689547264</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1101</v>
+        <v>1459</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>600.2737102051273</v>
+        <v>783.1046742038207</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.6</v>
+        <v>15.65</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>52.71968996515542</v>
+        <v>74.31105139639247</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.96600446287906</v>
+        <v>48.18547440080419</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.327371020512726</v>
+        <v>1.043948138210243</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0043640728272521</v>
+        <v>0.0013574940010528</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1504</v>
+        <v>1303</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>597.5990245904668</v>
+        <v>759.1085645981417</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>72.2</v>
+        <v>225.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.54009667563812</v>
+        <v>59.06717278943364</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.74209942142352</v>
+        <v>20.53475459873695</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4860647585770333</v>
+        <v>0.6310530529484822</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.030760448713893</v>
+        <v>2.240409168772285</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1315</v>
+        <v>1301</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>584.6515161599079</v>
+        <v>711.6869232320497</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>65.8</v>
+        <v>66</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.48424858382819</v>
+        <v>63.1051586694791</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>31.02271937801073</v>
+        <v>24.58308646548461</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2807823061498213</v>
+        <v>0.7827488138408241</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.06637363556886661</v>
+        <v>0.7888126802413464</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1301</v>
+        <v>1442</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>571.6869232320495</v>
+        <v>682.2900167238899</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.1051587043059</v>
+        <v>53.930893589086</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.58308652648188</v>
+        <v>18.01789547569421</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7827488138408241</v>
+        <v>1.178103357296245</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.7888126799170017</v>
+        <v>-0.0938671750463879</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1102</v>
+        <v>1312</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>562.190213179861</v>
+        <v>678.3153562304329</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>35.1</v>
+        <v>14.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.18913054404037</v>
+        <v>63.30526418897902</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.21986893642364</v>
+        <v>31.26725765030481</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4135146574790697</v>
+        <v>1.015305921195039</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.111920905982209</v>
+        <v>0.3192131118916075</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1459</v>
+        <v>1470</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>558.1046742038208</v>
+        <v>635.8117679098898</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.65</v>
+        <v>23.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>74.31105142599513</v>
+        <v>51.96057161164282</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>48.18547428568562</v>
+        <v>13.92909816156471</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.043948138210243</v>
+        <v>2.291585814344588</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0013574940010528</v>
+        <v>-0.9486749822173436</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1532</v>
+        <v>1503</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>553.1728258712883</v>
+        <v>610.0247756648364</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>23</v>
+        <v>207.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.8887791839559</v>
+        <v>53.46093876276608</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.6550109569934</v>
+        <v>16.8071570791417</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5513050917759128</v>
+        <v>0.7231221004130178</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0486937513451273</v>
+        <v>1.035432391938698</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1316</v>
+        <v>1232</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>550.6374852582943</v>
+        <v>607.1709520275838</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10.6</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>48.10030276986693</v>
+        <v>55.1182519125703</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>27.83857849538153</v>
+        <v>27.04379903907109</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5035868256456582</v>
+        <v>0.7106638699729712</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0463324212458553</v>
+        <v>-0.1545794225441028</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1312</v>
+        <v>1504</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>548.3153562304331</v>
+        <v>597.5990245904667</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.6</v>
+        <v>72.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.30526418238625</v>
+        <v>55.54009668722665</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.26725767809643</v>
+        <v>24.74209923895106</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.015305921195039</v>
+        <v>0.4860647585770333</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3192131118648976</v>
+        <v>-0.0307604486375816</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1470</v>
+        <v>1104</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>520.8117679098897</v>
+        <v>586.380250442442</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>23.9</v>
+        <v>27.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>51.96057162262335</v>
+        <v>64.46724914585988</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.9290981668611</v>
+        <v>14.85915098594078</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.291585814344588</v>
+        <v>0.5632760454284694</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.9486749822745812</v>
+        <v>0.1411783956476103</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1416</v>
+        <v>1315</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>520.3886424635651</v>
+        <v>584.6515161599079</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.75</v>
+        <v>65.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.14794352210915</v>
+        <v>56.48424855987045</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.72192887450618</v>
+        <v>31.02271936697581</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3420530265348266</v>
+        <v>0.2807823061498213</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0333478460334124</v>
+        <v>-0.066373635511614</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1439</v>
+        <v>1314</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>509.7117466677924</v>
+        <v>563.6963235952658</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>29.1</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.38856236553659</v>
+        <v>52.71417300803818</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>9.579898127930516</v>
+        <v>24.20368885833005</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2511043466674866</v>
+        <v>0.6992436086670154</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.1687176409972188</v>
+        <v>0.0413493804920739</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1503</v>
+        <v>1229</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>495.0247756648363</v>
+        <v>558.0838585270383</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>207.5</v>
+        <v>41.85</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.46093874536574</v>
+        <v>52.99314990051975</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.80715704794065</v>
+        <v>17.61071602655874</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7231221004130178</v>
+        <v>0.6540376114324904</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.035432392224902</v>
+        <v>0.0176670466642948</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1419</v>
+        <v>1532</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>458.4967356132143</v>
+        <v>553.1728258712883</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>23</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.94458680667017</v>
+        <v>56.88877910072191</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>17.24077257155451</v>
+        <v>21.65501107971405</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4777524206974257</v>
+        <v>0.5513050917759128</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1998621162820151</v>
+        <v>0.0486937513928301</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1455</v>
+        <v>1316</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>457.5816841675584</v>
+        <v>550.6374852582943</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.35347086438284</v>
+        <v>48.10030276986693</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.56268083095717</v>
+        <v>27.83857850967445</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5614132991404767</v>
+        <v>0.5035868256456582</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0120889079504896</v>
+        <v>-0.0463324212267774</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>457.29001672389</v>
+        <v>546.5129373437322</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>53.93089368768509</v>
+        <v>51.26192310743935</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18.01789545430698</v>
+        <v>19.84988252103924</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.178103357296245</v>
+        <v>0.8853154338649251</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.09386717514178659</v>
+        <v>0.0434961647797389</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1314</v>
+        <v>1472</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>448.6963235952658</v>
+        <v>544.6793587781294</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.71417303558376</v>
+        <v>52.10997352150133</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.20368894799046</v>
+        <v>7.771836037815946</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6992436086670154</v>
+        <v>0.804939786537715</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.041349380469179</v>
+        <v>0.947665757384674</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1104</v>
+        <v>1540</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>446.3802504424416</v>
+        <v>543.7906494069185</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>27.7</v>
+        <v>19.85</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>64.46724908626949</v>
+        <v>51.95357151048464</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.85915096335577</v>
+        <v>17.9213782535434</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5632760454284694</v>
+        <v>0.8094763803380755</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1411783956857671</v>
+        <v>0.1553950592585056</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1531</v>
+        <v>1219</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>446.0537216504391</v>
+        <v>538.8319651001896</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.05</v>
+        <v>11.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>35.93684944469678</v>
+        <v>54.9296087669566</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.45897194837644</v>
+        <v>19.9289924623126</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6850022059090413</v>
+        <v>0.3459677694965503</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.142782908899229</v>
+        <v>0.0672466760830174</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1229</v>
+        <v>1473</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>443.0838585270383</v>
+        <v>537.531794493249</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>41.85</v>
+        <v>20.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.99314985860294</v>
+        <v>52.82113554495325</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17.61071597774196</v>
+        <v>6.306611966736751</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6540376114324904</v>
+        <v>0.5733112471162135</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.017667046673838</v>
+        <v>0.0267525762438543</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1339</v>
+        <v>1434</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>439.0877405920077</v>
+        <v>536.8669457061288</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>43</v>
+        <v>18.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.79129603777337</v>
+        <v>55.75894577834412</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>19.1134772848124</v>
+        <v>30.77901268979095</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7879054292958065</v>
+        <v>0.7499385927693085</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.3027279706225197</v>
+        <v>0.0559582712072548</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1434</v>
+        <v>1514</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>421.8669457061289</v>
+        <v>536.062287080147</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.2</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.75894591604541</v>
+        <v>47.23616234114044</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30.77901265655384</v>
+        <v>17.39765136655937</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7499385927693085</v>
+        <v>0.735344455930585</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0559582711690954</v>
+        <v>0.4502163016156575</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1514</v>
+        <v>1439</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>421.062287080147</v>
+        <v>529.7117466677923</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>102</v>
+        <v>29.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.23616234114044</v>
+        <v>56.38856248493282</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.39765134092271</v>
+        <v>9.579898197739888</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.735344455930585</v>
+        <v>0.2511043466674866</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,11 +2319,11 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4502163017110514</v>
+        <v>-0.1687176410735351</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>411.0398508284878</v>
+        <v>526.0398508284883</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>746</v>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.38787890715391</v>
+        <v>54.38787887957393</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>14.17332687935145</v>
+        <v>14.17332692312058</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.8538773256110188</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.770961064740716</v>
+        <v>2.770961070846199</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1216</v>
+        <v>1455</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>408.5543871094739</v>
+        <v>522.5816841675584</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.25858622984109</v>
+        <v>55.35347093314461</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10.9830193062587</v>
+        <v>32.56268083917858</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5545527664461244</v>
+        <v>0.5614132991404767</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.1455610606532679</v>
+        <v>-0.0120889079676603</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1515</v>
+        <v>1416</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>408.2303646563909</v>
+        <v>520.3886424635651</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>30.8</v>
+        <v>11.75</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.30855787965719</v>
+        <v>59.14794352210915</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.3642434593136</v>
+        <v>27.72192887450618</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4196752140287684</v>
+        <v>0.3420530265348266</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.2633442408350186</v>
+        <v>-0.0333478460334124</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1513</v>
+        <v>1216</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>399.3093457753311</v>
+        <v>519.0153359579648</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>165.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.08569855081005</v>
+        <v>45.25858614504185</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.97709115519227</v>
+        <v>10.98301950571582</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.429718978344716</v>
+        <v>0.6006476512952194</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.2048291231344594</v>
+        <v>-0.1455610605769519</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1517</v>
+        <v>1476</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>395.1813836644727</v>
+        <v>518.0142530785082</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>10.95</v>
+        <v>313</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,29 +2566,29 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.1354951542237</v>
+        <v>40.90589415458433</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>30.95489419042001</v>
+        <v>18.78161894017571</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5103740596363729</v>
+        <v>0.7393780508317631</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0806796059394949</v>
+        <v>0.0553852950611091</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>389.9560211882261</v>
+        <v>504.9560211882261</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>14.15</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.02081889409557</v>
+        <v>54.02081890373549</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.80347714175953</v>
+        <v>26.80347712585812</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.6062085669346046</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.08433261689984831</v>
+        <v>0.0843326169284678</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1340</v>
+        <v>1215</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>389.820938587106</v>
+        <v>501.4164336366737</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5.23</v>
+        <v>110.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.03215022404468</v>
+        <v>55.38571840224716</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.68898710239227</v>
+        <v>16.82031150265955</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.847065948905365</v>
+        <v>0.6374186303564353</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.009438152202458401</v>
+        <v>0.2896281428840393</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1456</v>
+        <v>1340</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>386.5129373437323</v>
+        <v>499.820938587106</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>14</v>
+        <v>5.23</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.26192318349757</v>
+        <v>51.03215030763971</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.84988247793529</v>
+        <v>16.68898712706496</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8853154338649251</v>
+        <v>0.847065948905365</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0434961647701987</v>
+        <v>0.0094381522043663</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1215</v>
+        <v>1515</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>386.4164336366737</v>
+        <v>483.2303646563909</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>110.5</v>
+        <v>30.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.3857184311172</v>
+        <v>43.30855795227996</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.82031149846388</v>
+        <v>19.36424348614977</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6374186303564353</v>
+        <v>0.4196752140287684</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2896281428840393</v>
+        <v>-0.2633442409208755</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>381.9498647588754</v>
+        <v>481.3679811401539</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>7.7</v>
+        <v>52.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.69056544181819</v>
+        <v>40.7720298769591</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.59995352905524</v>
+        <v>31.63410386067315</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.1861515338802112</v>
+        <v>0.5034927410014666</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2075445234188468</v>
+        <v>0.0681420011889535</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1457</v>
+        <v>1419</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>379.0292802373673</v>
+        <v>478.4967356132149</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>14.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.40930716192582</v>
+        <v>53.94458686551241</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12.31330234645798</v>
+        <v>17.24077257990956</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.573516283889656</v>
+        <v>0.4777524206974257</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0061494188895958</v>
+        <v>0.1998621162247721</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1342</v>
+        <v>1103</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>378.9020223590667</v>
+        <v>476.8763921050037</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>102.5</v>
+        <v>13.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.71135880179283</v>
+        <v>54.36952870348063</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.9139164835805</v>
+        <v>17.2329793890346</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5346628232337114</v>
+        <v>0.7968160834400848</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1894059467745807</v>
+        <v>0.0198296677424297</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1323</v>
+        <v>1423</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>376.0886753966522</v>
+        <v>476.2055937430537</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>21.25</v>
+        <v>35.45</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.61111303203393</v>
+        <v>51.57402126017107</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.35167973433377</v>
+        <v>22.6910571059694</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1261114488591271</v>
+        <v>0.1088403182396261</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0754287260477432</v>
+        <v>-1.197851488149014</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1341</v>
+        <v>1409</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>373.5727531703784</v>
+        <v>474.5122324515265</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>59.5</v>
+        <v>24.55</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.13494248340554</v>
+        <v>50.72512617812334</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12.36431905899585</v>
+        <v>10.54479723282898</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4991554001408705</v>
+        <v>0.6572465714738357</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.509260592854999</v>
+        <v>0.0478463992546288</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1210</v>
+        <v>1438</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>371.3679811401539</v>
+        <v>473.7265229606172</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>52.2</v>
+        <v>22.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>40.77202976218034</v>
+        <v>51.44560453289358</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>31.63410380432993</v>
+        <v>8.097135522984948</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5034927410014666</v>
+        <v>0.7640070099479409</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0681420013034325</v>
+        <v>-0.0153144197870392</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1321</v>
+        <v>1517</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>364.018055885069</v>
+        <v>470.1813836644727</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>32.5</v>
+        <v>10.95</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.4011142879494</v>
+        <v>42.1354951663725</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.29797242414293</v>
+        <v>30.95489419042001</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5406046130855119</v>
+        <v>0.5103740596363729</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0378608281932766</v>
+        <v>-0.0806796059490351</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1438</v>
+        <v>1310</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>363.7265229606172</v>
+        <v>463.4963222973734</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>22.4</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.4456039751432</v>
+        <v>53.48029811066436</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8.09713548451608</v>
+        <v>20.69471960176562</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7640070099479409</v>
+        <v>0.8183182472139758</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0153144196344065</v>
+        <v>0.1263557632959913</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1103</v>
+        <v>1477</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>361.8763921050034</v>
+        <v>462.9523200915638</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>13.3</v>
+        <v>196.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.36952856594813</v>
+        <v>37.94420057758207</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.23297932903051</v>
+        <v>25.57387527279071</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7968160834400848</v>
+        <v>0.4874848047491461</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0198296677710486</v>
+        <v>-0.2514130719352607</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1423</v>
+        <v>1531</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>361.2055937430537</v>
+        <v>446.0537216504391</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>35.45</v>
+        <v>12.05</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.57402159960728</v>
+        <v>35.9368495539386</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.69105949498469</v>
+        <v>22.45897200950451</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1088403182396261</v>
+        <v>0.6850022059090413</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.197851495208407</v>
+        <v>-0.1427829089755461</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1409</v>
+        <v>1339</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>359.5122324515265</v>
+        <v>439.0877405920077</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>24.55</v>
+        <v>43</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.72512617812334</v>
+        <v>40.79129607497584</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10.54479724475158</v>
+        <v>19.11347731056175</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6572465714738357</v>
+        <v>0.7879054292958065</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0478463992546288</v>
+        <v>-0.302727970784693</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1560</v>
+        <v>1436</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>357.1145441144001</v>
+        <v>422.4907418590181</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>695</v>
+        <v>38.35</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.97636938651336</v>
+        <v>47.23102446364589</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8.982332868282239</v>
+        <v>16.03385176305959</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.240264838478367</v>
+        <v>0.509977052521186</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.8342481414546543</v>
+        <v>0.2209984958759768</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1477</v>
+        <v>1313</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>347.9523200915638</v>
+        <v>403.0425502600388</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>196.5</v>
+        <v>11.9</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>37.94420050827483</v>
+        <v>52.31434447570849</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.57387524877864</v>
+        <v>16.66364503247353</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4874848047491461</v>
+        <v>0.7056112676499469</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2514130709812967</v>
+        <v>0.0355030584646662</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1471</v>
+        <v>1513</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>337.6115126961608</v>
+        <v>399.3093457753306</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>9.74</v>
+        <v>165.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.02639886021014</v>
+        <v>51.08569853176564</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.99381358340203</v>
+        <v>11.97709115534101</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6098100653454555</v>
+        <v>0.429718978344716</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.023105140416309</v>
+        <v>-0.2048291229436626</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1108</v>
+        <v>1324</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>329.8011444894714</v>
+        <v>393.2031577570685</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11.65</v>
+        <v>10.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>33.98775167048593</v>
+        <v>48.50489034132379</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>48.83934990052571</v>
+        <v>14.27853901871351</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.546575721719492</v>
+        <v>2.283700498429956</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0349248244921067</v>
+        <v>0.0165793656091549</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1313</v>
+        <v>1568</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>328.0425502600388</v>
+        <v>389.6499446504505</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>11.9</v>
+        <v>29.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.31434444986113</v>
+        <v>50.67118065792354</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.66364511539674</v>
+        <v>9.942179499549813</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7056112676499469</v>
+        <v>1.188862253234526</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0355030583997958</v>
+        <v>0.1968640751121412</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1476</v>
+        <v>1213</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>328.0142530785084</v>
+        <v>381.9498647588754</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>313</v>
+        <v>7.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>40.90589392861627</v>
+        <v>52.690565443376</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.78161880664044</v>
+        <v>10.59995366405718</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7393780508317631</v>
+        <v>0.1861515338802112</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0553852981138112</v>
+        <v>0.2075445234283858</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>324.6793587781294</v>
+        <v>379.0292802373673</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.10997351375627</v>
+        <v>55.40930716192582</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7.771835991970092</v>
+        <v>12.31330234645798</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.804939786537715</v>
+        <v>1.573516283889656</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.947665757842582</v>
+        <v>0.0061494188895958</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1310</v>
+        <v>1342</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>323.4963222973734</v>
+        <v>378.9020223590667</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>102.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.48029810110853</v>
+        <v>44.71135888397036</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.69471960883353</v>
+        <v>15.91391646419596</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8183182472139758</v>
+        <v>0.5346628232337114</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1263557632692811</v>
+        <v>0.189405946602856</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1307</v>
+        <v>1338</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>322.2862545697274</v>
+        <v>376.4210265915214</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>30.45</v>
+        <v>14.45</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.66613194575029</v>
+        <v>37.67947827259748</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.79526219638399</v>
+        <v>42.77955212244095</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9974767492349782</v>
+        <v>0.3896806059232396</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0449830153993549</v>
+        <v>0.0527841886377066</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1203</v>
+        <v>1323</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>321.2670527446172</v>
+        <v>376.0886753966522</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>44.7</v>
+        <v>21.25</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.00678828276178</v>
+        <v>54.61111299385527</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.3115181508989</v>
+        <v>20.3516797406055</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.421883252815809</v>
+        <v>0.1261114488591271</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1121436527149062</v>
+        <v>-0.0754287260477432</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1447</v>
+        <v>1341</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>321.0565292447795</v>
+        <v>373.5727531703784</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>6.71</v>
+        <v>59.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.45967543300971</v>
+        <v>53.13494248524391</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.78282117786718</v>
+        <v>12.36431906065949</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8419026232183628</v>
+        <v>0.4991554001408705</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0014326396455216</v>
+        <v>1.509260592797754</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1528</v>
+        <v>1309</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>316.8459022502129</v>
+        <v>369.4163310529215</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>19.15</v>
+        <v>13.65</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.49308695371389</v>
+        <v>53.5138477999741</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.07328408678777</v>
+        <v>16.97474736675672</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8174896867379221</v>
+        <v>0.5702022474768377</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1358295682309084</v>
+        <v>0.1370938942022725</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1219</v>
+        <v>1321</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>313.8319651001896</v>
+        <v>364.018055885069</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11.6</v>
+        <v>32.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>54.92960875027718</v>
+        <v>51.40111427166969</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.9289924623126</v>
+        <v>13.29797245126976</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3459677694965503</v>
+        <v>0.5406046130855119</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0672466760830174</v>
+        <v>-0.0378608281837378</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1473</v>
+        <v>1305</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>312.531794493249</v>
+        <v>358.1558196550343</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20.1</v>
+        <v>12.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.82113545531578</v>
+        <v>51.31750290607517</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6.30661196989725</v>
+        <v>15.67953790605271</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5733112471162135</v>
+        <v>1.179400004891773</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0267525762915527</v>
+        <v>0.0710881757566455</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1436</v>
+        <v>1560</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>312.490741859018</v>
+        <v>357.1145441144001</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>38.35</v>
+        <v>695</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.23102461601099</v>
+        <v>49.97636941300761</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.03385181979581</v>
+        <v>8.982332995168958</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.509977052521186</v>
+        <v>1.240264838478367</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.220998496352961</v>
+        <v>0.8342481410730498</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1256</v>
+        <v>1524</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>312.0400678957125</v>
+        <v>356.1226749274601</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>173</v>
+        <v>26.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.96504791078424</v>
+        <v>43.60491346039576</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.40219419952395</v>
+        <v>17.16135075663744</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9462605070822492</v>
+        <v>0.8585462693516083</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6771541266481227</v>
+        <v>-0.0211687563545877</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1454</v>
+        <v>1410</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>305.4645002822335</v>
+        <v>350.2558940274287</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>12.15</v>
+        <v>24.55</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>38.15318098375158</v>
+        <v>40.1838955934893</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30.38509736019164</v>
+        <v>10.32170850834575</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.711368762750802</v>
+        <v>1.484148634952565</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0252489927168954</v>
+        <v>-0.0520001733420055</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1435</v>
+        <v>1220</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>304.8400523025255</v>
+        <v>347.1355533162478</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>22</v>
+        <v>10.7</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.3131253482809</v>
+        <v>28.14554096767131</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>6.177036826572684</v>
+        <v>29.32236961171503</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.630884176953517</v>
+        <v>0.4120313772459658</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.259299335570271</v>
+        <v>-0.0068440966940421</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1217</v>
+        <v>1203</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>301.5215840782629</v>
+        <v>341.2670527446172</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.35955753949767</v>
+        <v>48.00678828566421</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.56976707280108</v>
+        <v>13.31151819377588</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.002315269609481</v>
+        <v>1.421883252815809</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0038839787426088</v>
+        <v>-0.1121436527530593</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1582</v>
+        <v>1471</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>297.836573076433</v>
+        <v>337.6115126961608</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.60897629061822</v>
+        <v>48.02639891031971</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.513546952655</v>
+        <v>29.99381358646331</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5766127496171458</v>
+        <v>0.6098100653454555</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2132248014822997</v>
+        <v>0.0231051403972306</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1201</v>
+        <v>1108</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>297.1383571948839</v>
+        <v>329.8011444894714</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.25</v>
+        <v>11.65</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.07679253454349</v>
+        <v>33.98775167048593</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6.669955899789825</v>
+        <v>48.83934990052571</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.393238802899994</v>
+        <v>1.546575721719492</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0005164367236274</v>
+        <v>0.0349248244825664</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1325</v>
+        <v>1304</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>296.8312615935762</v>
+        <v>329.0668369916339</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>25.5</v>
+        <v>12.35</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.13304433472882</v>
+        <v>51.3420488517913</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.71167032200215</v>
+        <v>18.78356180262363</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7323514662238263</v>
+        <v>0.7503847866011439</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1019776141839137</v>
+        <v>0.0909895548150625</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1529</v>
+        <v>1435</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>295.8209201859999</v>
+        <v>324.8400523025255</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>16.45</v>
+        <v>22</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>33.67636419084647</v>
+        <v>47.313166381385</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>34.0087234999684</v>
+        <v>6.177040640302279</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.445530012231937</v>
+        <v>1.630884176953517</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.08356354467870949</v>
+        <v>-0.2592994230200906</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1540</v>
+        <v>1307</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>293.7906494069185</v>
+        <v>322.2862545697274</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>19.85</v>
+        <v>30.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.9535722626156</v>
+        <v>41.66613202036795</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.92137824914714</v>
+        <v>21.79526224018434</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8094763803380755</v>
+        <v>0.9974767492349782</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1553950592203475</v>
+        <v>0.0449830153611954</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>292.9030291185429</v>
+        <v>321.5215840782629</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>28</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.32208876765044</v>
+        <v>49.3595573728102</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18.58780826309214</v>
+        <v>15.5697673188957</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6168616400419953</v>
+        <v>1.002315269609481</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.003994531056193</v>
+        <v>-0.0038839787235294</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1460</v>
+        <v>1447</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>289.3295073641833</v>
+        <v>321.0565292447795</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>6.6</v>
+        <v>6.71</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.74162817842839</v>
+        <v>41.45967543300971</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.89222455623656</v>
+        <v>11.78282118302928</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.204090781455518</v>
+        <v>0.8419026232183628</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0104947352734185</v>
+        <v>-0.0014326396417055</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1475</v>
+        <v>1528</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>288.8220091031973</v>
+        <v>316.8459022502128</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>26.4</v>
+        <v>19.15</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.41404071984949</v>
+        <v>48.49308699805682</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.34650235171598</v>
+        <v>19.07328411201672</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3703743713280853</v>
+        <v>0.8174896867379221</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0421850477962505</v>
+        <v>0.135829568192749</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1525</v>
+        <v>1256</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>286.2777534780909</v>
+        <v>312.0400678957125</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>173</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.30049674448123</v>
+        <v>39.96504794303368</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.98477616782097</v>
+        <v>13.40219418066732</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.919545116377936</v>
+        <v>0.9462605070822492</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1159623021768439</v>
+        <v>-0.6771541266481227</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1541</v>
+        <v>1460</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>285.4897124879973</v>
+        <v>309.3295073641833</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>21.3</v>
+        <v>6.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>43.66113522702011</v>
+        <v>43.74162817091396</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>26.63303212462885</v>
+        <v>10.89222456652376</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4427698707408173</v>
+        <v>1.204090781455518</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0439695872060918</v>
+        <v>0.0104947352562476</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1324</v>
+        <v>1454</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>283.2031577570686</v>
+        <v>305.4645002822355</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10.1</v>
+        <v>12.15</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.50489043656457</v>
+        <v>38.15318113533303</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.27853904718056</v>
+        <v>30.38509744436311</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.283700498429956</v>
+        <v>0.711368762750802</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0165793655900749</v>
+        <v>-0.0252489927836722</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1521</v>
+        <v>1582</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>275.4312752894618</v>
+        <v>297.836573076433</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>25.75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.24328879578742</v>
+        <v>48.60897631641318</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.10320872225155</v>
+        <v>15.513546952655</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.012270557870604</v>
+        <v>0.5766127496171458</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0208850495833628</v>
+        <v>0.2132248013487466</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1568</v>
+        <v>1201</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>274.6499446504505</v>
+        <v>297.1383571948839</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>29.45</v>
+        <v>12.25</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.67118065792354</v>
+        <v>49.07679264162929</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.942179484294916</v>
+        <v>6.669955869654912</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.188862253234526</v>
+        <v>1.393238802899994</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1968640751121412</v>
+        <v>-0.0005164367236274</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1437</v>
+        <v>1325</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>272.8387333160049</v>
+        <v>296.8312615935762</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>32.05</v>
+        <v>25.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>59.40544047396622</v>
+        <v>43.13304431819271</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.81061567187442</v>
+        <v>21.71167033309529</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.0891469035182593</v>
+        <v>0.7323514662238263</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0194677442262863</v>
+        <v>-0.1019776141743687</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1109</v>
+        <v>1529</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>270.7042319395599</v>
+        <v>295.8209201859999</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>13.5</v>
+        <v>16.45</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.42490736641808</v>
+        <v>33.67636407926987</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>25.04879679271927</v>
+        <v>34.00872374499158</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.795509391332633</v>
+        <v>1.445530012231937</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0159888165728094</v>
+        <v>0.083563544793189</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1338</v>
+        <v>1233</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>261.4210265915213</v>
+        <v>292.9030291185429</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14.45</v>
+        <v>28</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.67947850060372</v>
+        <v>43.32208882766345</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>42.77955217296286</v>
+        <v>18.58780826309214</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3896806059232396</v>
+        <v>0.6168616400419953</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0527841886377066</v>
+        <v>0.003994531056193</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1536</v>
+        <v>1475</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>257.9095598024749</v>
+        <v>288.8220091031972</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>49.8</v>
+        <v>26.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.57602111483829</v>
+        <v>49.41404075915478</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.69079013486488</v>
+        <v>14.34650231149823</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9974903484806532</v>
+        <v>0.3703743713280853</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0796714591152833</v>
+        <v>0.0421850477199323</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>257.4275522482488</v>
+        <v>286.2777534780907</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>32.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.60385424999365</v>
+        <v>45.30050796115452</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8.8268587957575</v>
+        <v>16.98478380848175</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5138244411723669</v>
+        <v>1.919545116377936</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0147222916528674</v>
+        <v>-0.1159623138916218</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1466</v>
+        <v>1541</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>251.4682449145845</v>
+        <v>285.4897124879972</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>15.95</v>
+        <v>21.3</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.69337680289717</v>
+        <v>43.6611353470207</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.42472127733612</v>
+        <v>26.63303228553206</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.322333830811748</v>
+        <v>0.4427698707408173</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0270412372554005</v>
+        <v>-0.0439695875972205</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1414</v>
+        <v>1521</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>250.9088948409725</v>
+        <v>275.4312752894618</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>17.85</v>
+        <v>25.75</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>36.65374073306333</v>
+        <v>52.24328892361762</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.38817878275505</v>
+        <v>11.10320882490349</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.676104363886707</v>
+        <v>1.012270557870604</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2532020330806314</v>
+        <v>0.0208850495452031</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1524</v>
+        <v>1437</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>246.1226749274601</v>
+        <v>272.8387333160049</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>26.9</v>
+        <v>32.05</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.60491333601094</v>
+        <v>59.40544048789607</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.16135071977148</v>
+        <v>15.81061572566596</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8585462693516083</v>
+        <v>0.0891469035182593</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0211687563164269</v>
+        <v>-0.0194677442358225</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1526</v>
+        <v>1109</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>245.906727835436</v>
+        <v>270.7042319395598</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15.75</v>
+        <v>13.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.88000682744845</v>
+        <v>42.42490736641808</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.69124664385557</v>
+        <v>25.04879674863463</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.290699283592686</v>
+        <v>0.795509391332633</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1870964231364714</v>
+        <v>0.0159888165632695</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1537</v>
+        <v>1463</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>244.7752829647896</v>
+        <v>258.3864758510567</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>115.5</v>
+        <v>17.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>17.92731362191211</v>
+        <v>43.5351911399565</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>36.61603322885259</v>
+        <v>15.08207432458087</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.177528296478961</v>
+        <v>0.3748067538764144</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.56192116662817</v>
+        <v>-0.0188731325443129</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1305</v>
+        <v>1536</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>243.1558196550343</v>
+        <v>257.9095598024749</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>12.2</v>
+        <v>49.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.31750292178797</v>
+        <v>48.57602119319933</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.67953793908588</v>
+        <v>14.6907901307152</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.179400004891773</v>
+        <v>0.9974903484806532</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.071088175695592</v>
+        <v>-0.07967145921067451</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>242.5739278963758</v>
+        <v>257.4275522482489</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>30.95</v>
+        <v>32.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>37.8247901129362</v>
+        <v>45.60385434271409</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.83808191711777</v>
+        <v>8.826858817921796</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7658522005793698</v>
+        <v>0.5138244411723669</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0498547373442074</v>
+        <v>0.0147222916242486</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1225</v>
+        <v>1451</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>239.3380172681004</v>
+        <v>253.8299642524928</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>25</v>
+        <v>17.25</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.65066221196571</v>
+        <v>44.12378015256455</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>23.19351353482199</v>
+        <v>20.51141259135586</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.835680004093106</v>
+        <v>0.4559409008928521</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.131292480923818</v>
+        <v>-0.0196286634076048</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1444</v>
+        <v>1466</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>239.171169942622</v>
+        <v>251.4682449145845</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>7.09</v>
+        <v>15.95</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.98859794047429</v>
+        <v>46.69337686437706</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.06941157326651</v>
+        <v>11.4247212751115</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.29768496276175</v>
+        <v>0.322333830811748</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0070432373175376</v>
+        <v>-0.0270412373126373</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1463</v>
+        <v>1414</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>238.3864758510567</v>
+        <v>250.9088948409725</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>17.4</v>
+        <v>17.85</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.53519106578492</v>
+        <v>36.65374067259414</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.08207432458087</v>
+        <v>19.38817876635891</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3748067538764144</v>
+        <v>0.676104363886707</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0188731325347735</v>
+        <v>-0.2532020331460288</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1220</v>
+        <v>1526</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>237.1355533162478</v>
+        <v>245.906727835436</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>10.7</v>
+        <v>15.75</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>28.14554089501108</v>
+        <v>40.88000686012085</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>29.32236941694267</v>
+        <v>20.69124669976623</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4120313772459658</v>
+        <v>0.290699283592686</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0068440966940421</v>
+        <v>-0.1870964231269327</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1522</v>
+        <v>1445</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>236.0157396608762</v>
+        <v>245.7812803270787</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>26.95</v>
+        <v>10.15</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>35.15537787911811</v>
+        <v>40.81736990371029</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.38638701503171</v>
+        <v>11.15608646982731</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.173577660936783</v>
+        <v>1.341771008280132</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0711449640609312</v>
+        <v>0.0159247238922333</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1451</v>
+        <v>1537</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>233.8299642524928</v>
+        <v>244.7752829647896</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17.25</v>
+        <v>115.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.12378018958584</v>
+        <v>17.92731356716601</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.5114125545437</v>
+        <v>36.61603331829296</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4559409008928521</v>
+        <v>1.177528296478961</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.019628663398064</v>
+        <v>-0.5619211665327746</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1418</v>
+        <v>1464</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>230.7903877357448</v>
+        <v>243.7446875485736</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>17.6</v>
+        <v>10.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>40.93810872079176</v>
+        <v>41.68184092112934</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.6332811448221</v>
+        <v>13.00767858133265</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5485919003939944</v>
+        <v>0.8383267820946402</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.01344844695116</v>
+        <v>-0.0115886009869929</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1309</v>
+        <v>1533</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>229.4163310529215</v>
+        <v>242.5739278963758</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.65</v>
+        <v>30.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>53.51384781893382</v>
+        <v>37.82479009745801</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.97474737641485</v>
+        <v>22.8380819324495</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5702022474768377</v>
+        <v>0.7658522005793698</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1370938941450348</v>
+        <v>0.0498547373060462</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1453</v>
+        <v>1225</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>229.1145325834808</v>
+        <v>239.3380172681004</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>11.15</v>
+        <v>25</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.27616755749921</v>
+        <v>45.65066229044582</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.2895411811274</v>
+        <v>23.19351348378779</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.519210586356377</v>
+        <v>1.835680004093106</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0208347689817452</v>
+        <v>0.1312924808665787</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1410</v>
+        <v>1444</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>215.2558940274287</v>
+        <v>239.171169942622</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>24.55</v>
+        <v>7.09</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.18388272470583</v>
+        <v>42.98859795254366</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.32170437683952</v>
+        <v>19.06941154780512</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.484148634952565</v>
+        <v>1.29768496276175</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0520001666642003</v>
+        <v>0.0070432373118133</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>213.8812730478359</v>
+        <v>236.0157396608759</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>28.25</v>
+        <v>26.95</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.73704625613079</v>
+        <v>35.15537791529897</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.20478449082862</v>
+        <v>14.38638703786072</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5657523675903192</v>
+        <v>1.173577660936783</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0627989162458274</v>
+        <v>-0.0711449641467878</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1446</v>
+        <v>1418</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>211.436863580719</v>
+        <v>230.7903877357448</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>13.4</v>
+        <v>17.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>29.0324374312776</v>
+        <v>40.9381084883661</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>35.08063965553796</v>
+        <v>13.63328115941041</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6992597239257102</v>
+        <v>0.5485919003939944</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0334423241420104</v>
+        <v>-0.0134484469225377</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1413</v>
+        <v>1453</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>208.7176173932031</v>
+        <v>229.1145325834808</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>9.19</v>
+        <v>11.15</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.38254654571875</v>
+        <v>47.2761675798092</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>9.283416810419681</v>
+        <v>20.28954124398216</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.167238053077312</v>
+        <v>0.519210586356377</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0188536053630114</v>
+        <v>-0.0208347690008248</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1516</v>
+        <v>1530</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>207.6702604485639</v>
+        <v>213.8812730478359</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14.35</v>
+        <v>28.25</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.69792550900666</v>
+        <v>43.73704632420892</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>22.18179759534365</v>
+        <v>12.20478451507669</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.1009936979042695</v>
+        <v>0.5657523675903192</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.1947905579525922</v>
+        <v>-0.0627989163412241</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1417</v>
+        <v>1446</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>207.0570731782976</v>
+        <v>211.436863580719</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.48805159957224</v>
+        <v>29.03243728963476</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.74313195581221</v>
+        <v>35.08063963677308</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7810863259812616</v>
+        <v>0.6992597239257102</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0137089195902389</v>
+        <v>0.0334423241610906</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1535</v>
+        <v>1413</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>192.4368563376292</v>
+        <v>208.7176173932031</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>45.35</v>
+        <v>9.19</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>34.52739993715832</v>
+        <v>44.38254659529574</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11.4687457294166</v>
+        <v>9.283416825922998</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5874104041042792</v>
+        <v>1.167238053077312</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0295976287313043</v>
+        <v>-0.0188536053725511</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>191.6626068150529</v>
+        <v>207.6702604485639</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>6.25</v>
+        <v>14.35</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>32.0498595961669</v>
+        <v>48.69792550900666</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.176192772893687</v>
+        <v>22.18179760998663</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.161697031574855</v>
+        <v>0.1009936979042695</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0231255542743347</v>
+        <v>0.1947905579239718</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1304</v>
+        <v>1417</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>189.0668369916338</v>
+        <v>207.0570731782976</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>12.35</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>51.3420488517913</v>
+        <v>45.48805157639007</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.78356183873358</v>
+        <v>13.7431319844846</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7503847866011439</v>
+        <v>0.7810863259812616</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0909895547730869</v>
+        <v>0.0137089195864241</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>183.767773727626</v>
+        <v>196.992858347383</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.35</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.38984155109282</v>
+        <v>41.20680836225966</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.29018876642661</v>
+        <v>15.13954619933706</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.925795948908382</v>
+        <v>1.092708901844937</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.014885695046892</v>
+        <v>0.0113580809677398</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>178.6179415176655</v>
+        <v>192.4368563376292</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>15.6</v>
+        <v>45.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.82999954873394</v>
+        <v>34.52739998671566</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.9096022651522</v>
+        <v>11.46874570628787</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.163314294776451</v>
+        <v>0.5874104041042792</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0217410399648175</v>
+        <v>0.0295976286740657</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1467</v>
+        <v>1512</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>173.6662830313327</v>
+        <v>191.6626068150529</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>8.19</v>
+        <v>6.25</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.04359216126117</v>
+        <v>32.04985949529673</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>9.987704040274256</v>
+        <v>9.176192791692417</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7081178324521233</v>
+        <v>1.161697031574855</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0273274651305928</v>
+        <v>-0.0231255542743347</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1218</v>
+        <v>1452</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>158.4345757981756</v>
+        <v>183.767773727626</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>14.45</v>
+        <v>11.35</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>48.90439074902242</v>
+        <v>46.38984166330875</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.41304999246757</v>
+        <v>17.29018877033496</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5580914661317187</v>
+        <v>0.925795948908382</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1369753162647474</v>
+        <v>-0.0148856950564308</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>149.3200283335068</v>
+        <v>178.6179415176655</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.94801374913052</v>
+        <v>40.82999967426503</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.853224888910344</v>
+        <v>11.9096023012493</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3341252203233964</v>
+        <v>1.163314294776451</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0505788257243882</v>
+        <v>-0.0217410399934359</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1227</v>
+        <v>1467</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>143.1294908224828</v>
+        <v>173.6662830313327</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>28.55</v>
+        <v>8.19</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.9615124485523</v>
+        <v>40.04359217109668</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.24896268134929</v>
+        <v>9.987704074501371</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5517726837800515</v>
+        <v>0.7081178324521233</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0277513651005817</v>
+        <v>-0.027327465132501</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1445</v>
+        <v>1218</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>135.7812803270787</v>
+        <v>158.4345757981756</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>10.15</v>
+        <v>14.45</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>40.81736980894895</v>
+        <v>48.90439079266819</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>11.15608643590447</v>
+        <v>13.41305009990726</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.341771008280132</v>
+        <v>0.5580914661317187</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0159247239494715</v>
+        <v>0.1369753161311918</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1464</v>
+        <v>1538</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>133.7446875485736</v>
+        <v>149.3200283335068</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>41.68184085371609</v>
+        <v>45.94801441980419</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.00767859933166</v>
+        <v>9.853224843346394</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.8383267820946402</v>
+        <v>0.3341252203233964</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0115886009679137</v>
+        <v>-0.0505788257243882</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1506</v>
+        <v>1227</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>133.2763110181325</v>
+        <v>143.1294908224828</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>10.1</v>
+        <v>28.55</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>43.64927625366833</v>
+        <v>42.9615123827078</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.48733820874447</v>
+        <v>13.24896291268792</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7908710651418391</v>
+        <v>0.5517726837800515</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0064448844964832</v>
+        <v>-0.0277513650624214</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1474</v>
+        <v>1506</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>116.1895353238607</v>
+        <v>133.2763110181325</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.21708583611354</v>
+        <v>43.64927619988803</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.72510856236737</v>
+        <v>11.48733821201426</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.3471352893400194</v>
+        <v>0.7908710651418391</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0071540680836225</v>
+        <v>-0.0064448844964832</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1231</v>
+        <v>1474</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>115.1176335738917</v>
+        <v>116.1895353238607</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>10</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>41.57773687546849</v>
+        <v>44.21708599705301</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>13.48793891524365</v>
+        <v>11.72510856225319</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.9794257515555276</v>
+        <v>0.3471352893400194</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.1350988233457601</v>
+        <v>0.0071540680740827</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1468</v>
+        <v>1231</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>106.3281308250252</v>
+        <v>115.1176335738916</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>13</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45.3396748265702</v>
+        <v>41.57773683212475</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>14.14861044838885</v>
+        <v>13.48793918072535</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.032813082502524</v>
+        <v>0.9794257515555276</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0543234998080848</v>
+        <v>0.1350988235365589</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1443</v>
+        <v>1468</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>105.869685993482</v>
+        <v>106.3281308250252</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>23.7</v>
+        <v>13</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>47.67070344310725</v>
+        <v>45.33967487899312</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>5.607369832428579</v>
+        <v>14.14861044838885</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.434089214735004</v>
+        <v>1.032813082502524</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0135112895490165</v>
+        <v>-0.0543234998271644</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1465</v>
+        <v>1443</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>97.10866428485154</v>
+        <v>105.8696859934815</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>11.9</v>
+        <v>23.7</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>40.2905379265347</v>
+        <v>47.67070343174935</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.49969581643431</v>
+        <v>5.607369871737686</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.7051050586527078</v>
+        <v>1.434089214735004</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.004725792348574</v>
+        <v>-0.0135112895299352</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1432</v>
+        <v>1465</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>86.99285834738302</v>
+        <v>97.10866428485154</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>15</v>
+        <v>11.9</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>41.2068082117759</v>
+        <v>40.29053794994378</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15.13954623736804</v>
+        <v>17.49969575951642</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.092708901844937</v>
+        <v>0.7051050586527078</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0113580809868186</v>
+        <v>0.004725792348574</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>84.81645875242556</v>
+        <v>84.81645875242548</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>8.800000000000001</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>43.06483437160058</v>
+        <v>43.06483450300362</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>13.79160517817989</v>
+        <v>13.79160525334734</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.8816759882453313</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0077818114306195</v>
+        <v>-0.0077818114401597</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
